--- a/smartcards_Testdecks.xlsx
+++ b/smartcards_Testdecks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\04_SmartCards_Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED362CB-0B53-4B96-831C-4E02548A55F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59C975E-F117-44DF-83A9-EB43F57EB2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
     <sheet name="config" sheetId="7" r:id="rId3"/>
     <sheet name="Hauptstädte" sheetId="3" r:id="rId4"/>
     <sheet name="Alter Peter" sheetId="8" r:id="rId5"/>
-    <sheet name="Mathematik" sheetId="4" r:id="rId6"/>
+    <sheet name="Deutschland" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="229">
   <si>
     <t>SmartCards – Anleitung zur xlsx-Befüllung</t>
   </si>
@@ -216,69 +216,6 @@
     <t>Ozeanien</t>
   </si>
   <si>
-    <t>SmartCards – Mathematik</t>
-  </si>
-  <si>
-    <t>Kleines Einmaleins zum Üben.</t>
-  </si>
-  <si>
-    <t>2 × 3</t>
-  </si>
-  <si>
-    <t>Einmaleins</t>
-  </si>
-  <si>
-    <t>2 × 4</t>
-  </si>
-  <si>
-    <t>3 × 3</t>
-  </si>
-  <si>
-    <t>3 × 4</t>
-  </si>
-  <si>
-    <t>4 × 4</t>
-  </si>
-  <si>
-    <t>5 × 5</t>
-  </si>
-  <si>
-    <t>6 × 6</t>
-  </si>
-  <si>
-    <t>7 × 7</t>
-  </si>
-  <si>
-    <t>8 × 8</t>
-  </si>
-  <si>
-    <t>9 × 9</t>
-  </si>
-  <si>
-    <t>6 × 7</t>
-  </si>
-  <si>
-    <t>7 × 8</t>
-  </si>
-  <si>
-    <t>8 × 9</t>
-  </si>
-  <si>
-    <t>9 × 6</t>
-  </si>
-  <si>
-    <t>3 × 9</t>
-  </si>
-  <si>
-    <t>4 × 7</t>
-  </si>
-  <si>
-    <t>5 × 8</t>
-  </si>
-  <si>
-    <t>2 × 9</t>
-  </si>
-  <si>
     <t>Zeit</t>
   </si>
   <si>
@@ -382,9 +319,6 @@
   </si>
   <si>
     <t>Deck mit Abfrage</t>
-  </si>
-  <si>
-    <t>Mathematik</t>
   </si>
   <si>
     <t>Es ist die einzige nennenswerte Erhebung innerhalb der historischen Münchner Altstadt.</t>
@@ -539,6 +473,252 @@
   </si>
   <si>
     <t>https://alterpeter.de/wp-content/uploads/2021/10/03_Das_Treppenhaus_im_Alten_Peter_bei_Nacht.jpg</t>
+  </si>
+  <si>
+    <t>Bremen besteht aus zwei Städten: Bremen und Bremerhaven.</t>
+  </si>
+  <si>
+    <t>Bremen ist nur etwa 419 km² groß und hat rund 680.000 Einwohner.</t>
+  </si>
+  <si>
+    <t>Bundesländer im Vergleich</t>
+  </si>
+  <si>
+    <t>Bremen</t>
+  </si>
+  <si>
+    <t>Welches ist das kleinste Bundesland – sowohl nach Fläche als auch nach Einwohnerzahl?</t>
+  </si>
+  <si>
+    <t>Damit lebt fast jeder fünfte Mensch in Deutschland in NRW.</t>
+  </si>
+  <si>
+    <t>Nordrhein-Westfalen, mit über 18 Millionen Menschen</t>
+  </si>
+  <si>
+    <t>Welches Bundesland hat die meisten Einwohner?</t>
+  </si>
+  <si>
+    <t>Bayern hat außerdem über 13 Millionen Einwohner – das sind mehr als in jedem anderen Bundesland außer NRW.</t>
+  </si>
+  <si>
+    <t>Bayern, etwa 70.550 km²</t>
+  </si>
+  <si>
+    <t>Welches ist das flächengrößte Bundesland und wie groß ist es?</t>
+  </si>
+  <si>
+    <t>Das Gebäude wurde vom Architekten Norman Foster entworfen.</t>
+  </si>
+  <si>
+    <t>Fast alle deutschen Wolkenkratzer über 150 Meter Höhe stehen in Frankfurt.</t>
+  </si>
+  <si>
+    <t>Rekorde</t>
+  </si>
+  <si>
+    <t>Commerzbank Tower in Frankfurt am Main, 259 Meter</t>
+  </si>
+  <si>
+    <t>Wie heißt das höchste Gebäude Deutschlands und wie hoch ist es?</t>
+  </si>
+  <si>
+    <t>Sie ist 2.962 Meter hoch und liegt in den bayerischen Alpen.</t>
+  </si>
+  <si>
+    <t>Zugspitze</t>
+  </si>
+  <si>
+    <t>Wie heißt der höchste Berg Deutschlands?</t>
+  </si>
+  <si>
+    <t>Er entspringt in der Schweiz und mündet in den Niederlanden in die Nordsee.</t>
+  </si>
+  <si>
+    <t>Er ist auf deutschem Gebiet etwa 1.233 km lang.</t>
+  </si>
+  <si>
+    <t>Rhein</t>
+  </si>
+  <si>
+    <t>Wie heißt der längste Fluss Deutschlands?</t>
+  </si>
+  <si>
+    <t>Der größte See, der komplett in Deutschland liegt, ist die Müritz in Mecklenburg-Vorpommern.</t>
+  </si>
+  <si>
+    <t>Er liegt im Dreiländereck zwischen Deutschland, Österreich und der Schweiz.</t>
+  </si>
+  <si>
+    <t>Bodensee</t>
+  </si>
+  <si>
+    <t>Wie heißt der größte See Deutschlands?</t>
+  </si>
+  <si>
+    <t>Hauptstädte</t>
+  </si>
+  <si>
+    <t>Erfurt</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Thüringen?</t>
+  </si>
+  <si>
+    <t>Kiel</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Schleswig-Holstein?</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Sachsen-Anhalt?</t>
+  </si>
+  <si>
+    <t>Nicht zu verwechseln mit Leipzig, der größten Stadt Sachsens!</t>
+  </si>
+  <si>
+    <t>Dresden</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Sachsen?</t>
+  </si>
+  <si>
+    <t>Saarbrücken</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt vom Saarland?</t>
+  </si>
+  <si>
+    <t>Mainz</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Rheinland-Pfalz?</t>
+  </si>
+  <si>
+    <t>Nicht zu verwechseln mit Köln, der größten Stadt NRWs!</t>
+  </si>
+  <si>
+    <t>Düsseldorf</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Nordrhein-Westfalen?</t>
+  </si>
+  <si>
+    <t>Hannover</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Niedersachsen?</t>
+  </si>
+  <si>
+    <t>Schwerin</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Mecklenburg-Vorpommern?</t>
+  </si>
+  <si>
+    <t>Nicht zu verwechseln mit Frankfurt am Main, der größten Stadt Hessens!</t>
+  </si>
+  <si>
+    <t>Wiesbaden</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Hessen?</t>
+  </si>
+  <si>
+    <t>Auch Hamburg ist Bundesland und Hauptstadt in einem.</t>
+  </si>
+  <si>
+    <t>Hamburg</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Hamburg?</t>
+  </si>
+  <si>
+    <t>Bremen ist ebenfalls Bundesland und Hauptstadt zugleich.</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Bremen?</t>
+  </si>
+  <si>
+    <t>Potsdam</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Brandenburg?</t>
+  </si>
+  <si>
+    <t>Berlin ist außerdem die Hauptstadt von ganz Deutschland.</t>
+  </si>
+  <si>
+    <t>Berlin ist gleichzeitig Bundesland und Hauptstadt der Stadt.</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Berlin?</t>
+  </si>
+  <si>
+    <t>München</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Bayern?</t>
+  </si>
+  <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
+    <t>Wie heißt die Hauptstadt von Baden-Württemberg?</t>
+  </si>
+  <si>
+    <t>Er gehörte der FDP an.</t>
+  </si>
+  <si>
+    <t>Er war von 1949 bis 1959 Bundespräsident.</t>
+  </si>
+  <si>
+    <t>Grundlagen</t>
+  </si>
+  <si>
+    <t>Theodor Heuss</t>
+  </si>
+  <si>
+    <t>Wer war der erste Bundespräsident Deutschlands?</t>
+  </si>
+  <si>
+    <t>Er gehörte der CDU an.</t>
+  </si>
+  <si>
+    <t>Konrad Adenauer</t>
+  </si>
+  <si>
+    <t>Wer war der erste Bundeskanzler Deutschlands?</t>
+  </si>
+  <si>
+    <t>Die Wiedervereinigung mit der DDR folgte später, am 3. Oktober 1990.</t>
+  </si>
+  <si>
+    <t>An diesem Tag trat das Grundgesetz in Kraft.</t>
+  </si>
+  <si>
+    <t>23. Mai 1949</t>
+  </si>
+  <si>
+    <t>Wann wurde die Bundesrepublik Deutschland gegründet?</t>
+  </si>
+  <si>
+    <t>Drei davon sind Stadtstaaten: Berlin, Hamburg und Bremen.</t>
+  </si>
+  <si>
+    <t>Wie viele Bundesländer hat Deutschland?</t>
+  </si>
+  <si>
+    <t>Grundwissen, Bundesländer, Hauptstädte und geografische Rekorde rund um Deutschland.</t>
+  </si>
+  <si>
+    <t>SmartCards – Deutschland</t>
+  </si>
+  <si>
+    <t>Er war von 1949 bis 1963 im Amt</t>
   </si>
 </sst>
 </file>
@@ -658,7 +838,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -684,6 +864,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1084,59 +1265,59 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>20</v>
@@ -1144,13 +1325,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>20</v>
@@ -1159,140 +1340,140 @@
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="F11" s="7"/>
     </row>
@@ -1306,7 +1487,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.77734375" bestFit="1" customWidth="1"/>
@@ -1314,12 +1495,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1580,12 +1756,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1607,217 +1783,217 @@
     </row>
     <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="E6" s="11"/>
     </row>
     <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="B7" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="E9" s="11"/>
     </row>
     <row r="10" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>141</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>163</v>
       </c>
       <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="E17" s="11"/>
     </row>
@@ -1830,238 +2006,442 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBDE89F-70C0-49AC-AFE6-1132080C3BCF}">
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="5" width="40" customWidth="1"/>
+    <col min="1" max="1" width="55.77734375" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="5" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>63</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>64</v>
+      <c r="A2" s="13" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="12" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
+      <c r="A4" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="B4" s="15">
+        <v>16</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
+      <c r="A5" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
+      <c r="A6" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
+      <c r="A7" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
+      <c r="A8" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>66</v>
-      </c>
+      <c r="A9" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
+      <c r="A10" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
+      <c r="A11" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>66</v>
-      </c>
+      <c r="A12" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13">
-        <v>81</v>
-      </c>
-      <c r="C13" t="s">
-        <v>66</v>
-      </c>
+      <c r="A13" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14">
-        <v>42</v>
-      </c>
-      <c r="C14" t="s">
-        <v>66</v>
-      </c>
+      <c r="A14" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B15">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>66</v>
-      </c>
+      <c r="A15" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17">
-        <v>54</v>
-      </c>
-      <c r="C17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18">
-        <v>27</v>
-      </c>
-      <c r="C18" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19">
-        <v>28</v>
-      </c>
-      <c r="C19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21">
-        <v>18</v>
-      </c>
-      <c r="C21" t="s">
-        <v>66</v>
+      <c r="A16" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E20" s="11"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E26" s="11"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E28" s="11"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29" s="11"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/smartcards_Testdecks.xlsx
+++ b/smartcards_Testdecks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\04_SmartCards_Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59C975E-F117-44DF-83A9-EB43F57EB2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0D8C6D-6E6D-4B9A-80E0-08514C90AD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,20 @@
     <sheet name="Alter Peter" sheetId="8" r:id="rId5"/>
     <sheet name="Deutschland" sheetId="9" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -562,108 +575,63 @@
     <t>Erfurt</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Thüringen?</t>
-  </si>
-  <si>
     <t>Kiel</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Schleswig-Holstein?</t>
-  </si>
-  <si>
     <t>Magdeburg</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Sachsen-Anhalt?</t>
-  </si>
-  <si>
     <t>Nicht zu verwechseln mit Leipzig, der größten Stadt Sachsens!</t>
   </si>
   <si>
     <t>Dresden</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Sachsen?</t>
-  </si>
-  <si>
     <t>Saarbrücken</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt vom Saarland?</t>
-  </si>
-  <si>
     <t>Mainz</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Rheinland-Pfalz?</t>
-  </si>
-  <si>
     <t>Nicht zu verwechseln mit Köln, der größten Stadt NRWs!</t>
   </si>
   <si>
     <t>Düsseldorf</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Nordrhein-Westfalen?</t>
-  </si>
-  <si>
     <t>Hannover</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Niedersachsen?</t>
-  </si>
-  <si>
     <t>Schwerin</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Mecklenburg-Vorpommern?</t>
-  </si>
-  <si>
     <t>Nicht zu verwechseln mit Frankfurt am Main, der größten Stadt Hessens!</t>
   </si>
   <si>
     <t>Wiesbaden</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Hessen?</t>
-  </si>
-  <si>
     <t>Auch Hamburg ist Bundesland und Hauptstadt in einem.</t>
   </si>
   <si>
     <t>Hamburg</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Hamburg?</t>
-  </si>
-  <si>
     <t>Bremen ist ebenfalls Bundesland und Hauptstadt zugleich.</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Bremen?</t>
-  </si>
-  <si>
     <t>Potsdam</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Brandenburg?</t>
-  </si>
-  <si>
     <t>Berlin ist außerdem die Hauptstadt von ganz Deutschland.</t>
   </si>
   <si>
     <t>Berlin ist gleichzeitig Bundesland und Hauptstadt der Stadt.</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Berlin?</t>
-  </si>
-  <si>
     <t>München</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Bayern?</t>
-  </si>
-  <si>
     <t>Stuttgart</t>
   </si>
   <si>
@@ -719,6 +687,66 @@
   </si>
   <si>
     <t>Er war von 1949 bis 1963 im Amt</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Bayern?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Berlin?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Brandenburg?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Bremen?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Hamburg?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Hessen?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Mecklenburg-Vorpommern?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Thüringen?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Schleswig-Holstein?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Sachsen-Anhalt?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Sachsen?</t>
+  </si>
+  <si>
+    <t>Hauptstadt vom 
+Saarland?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Rheinland-Pfalz?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Nordrhein-Westfalen?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Niedersachsen?</t>
   </si>
 </sst>
 </file>
@@ -838,7 +866,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -864,7 +892,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -2018,12 +2045,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2045,76 +2072,76 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B4" s="15">
+        <v>210</v>
+      </c>
+      <c r="B4" s="11">
         <v>16</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>174</v>
@@ -2122,12 +2149,12 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>209</v>
+    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>214</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>174</v>
@@ -2135,9 +2162,9 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
-        <v>207</v>
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>215</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>19</v>
@@ -2146,18 +2173,18 @@
         <v>174</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
-        <v>204</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>216</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>174</v>
@@ -2165,9 +2192,9 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
-        <v>202</v>
+    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>217</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>150</v>
@@ -2176,46 +2203,46 @@
         <v>174</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E12" s="11"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
-        <v>200</v>
+    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>218</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>174</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
-        <v>197</v>
+    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>219</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>174</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E14" s="11"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
-        <v>194</v>
+    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>220</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>174</v>
@@ -2223,12 +2250,12 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
-        <v>192</v>
+    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>228</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>174</v>
@@ -2236,27 +2263,27 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
-        <v>190</v>
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>227</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>174</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
-        <v>187</v>
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="14" t="s">
+        <v>226</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>174</v>
@@ -2264,12 +2291,12 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
-        <v>185</v>
+    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
+        <v>225</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>174</v>
@@ -2277,27 +2304,27 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
-        <v>183</v>
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>224</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>174</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
-        <v>180</v>
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>223</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>174</v>
@@ -2305,12 +2332,12 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
-        <v>178</v>
+    <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>222</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>174</v>
@@ -2318,9 +2345,9 @@
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
-        <v>176</v>
+    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>221</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>175</v>

--- a/smartcards_Testdecks.xlsx
+++ b/smartcards_Testdecks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\04_SmartCards_Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0D8C6D-6E6D-4B9A-80E0-08514C90AD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF89C71-40ED-4BC5-B2A1-6B7F96C04B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -635,9 +635,6 @@
     <t>Stuttgart</t>
   </si>
   <si>
-    <t>Wie heißt die Hauptstadt von Baden-Württemberg?</t>
-  </si>
-  <si>
     <t>Er gehörte der FDP an.</t>
   </si>
   <si>
@@ -747,6 +744,10 @@
   <si>
     <t>Hauptstadt von 
 Niedersachsen?</t>
+  </si>
+  <si>
+    <t>Hauptstadt von 
+Baden-Württemberg?</t>
   </si>
 </sst>
 </file>
@@ -2045,12 +2046,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2072,73 +2073,73 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B4" s="11">
         <v>16</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>228</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>195</v>
@@ -2151,7 +2152,7 @@
     </row>
     <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>194</v>
@@ -2164,7 +2165,7 @@
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>19</v>
@@ -2181,7 +2182,7 @@
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>191</v>
@@ -2194,7 +2195,7 @@
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>150</v>
@@ -2209,7 +2210,7 @@
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>189</v>
@@ -2224,7 +2225,7 @@
     </row>
     <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>187</v>
@@ -2239,7 +2240,7 @@
     </row>
     <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>185</v>
@@ -2252,7 +2253,7 @@
     </row>
     <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>184</v>
@@ -2265,7 +2266,7 @@
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>183</v>
@@ -2280,7 +2281,7 @@
     </row>
     <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>181</v>
@@ -2293,7 +2294,7 @@
     </row>
     <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>180</v>
@@ -2306,7 +2307,7 @@
     </row>
     <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>179</v>
@@ -2321,7 +2322,7 @@
     </row>
     <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>177</v>
@@ -2334,7 +2335,7 @@
     </row>
     <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>176</v>
@@ -2347,7 +2348,7 @@
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>175</v>
